--- a/data/trans_bre/IP21B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Estudios-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-80,8; 0,0</t>
+          <t>-81,21; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-80,49; 0,0</t>
+          <t>-81,57; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 23,46</t>
+          <t>-12,75; 21,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 17,85</t>
+          <t>-17,13; 18,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 15,02</t>
+          <t>-30,69; 13,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,29; 29,55</t>
+          <t>-49,31; 25,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,94; 606,82</t>
+          <t>-79,85; 487,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,94; 250,65</t>
+          <t>-74,19; 361,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 48,26</t>
+          <t>-37,09; 50,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 63,39</t>
+          <t>-10,03; 58,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-63,58; 60,87</t>
+          <t>-62,38; 66,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 9,7</t>
+          <t>-14,51; 11,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 12,03</t>
+          <t>-16,32; 14,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 22,2</t>
+          <t>-20,79; 21,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 31,78</t>
+          <t>-30,15; 32,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,34; 201,84</t>
+          <t>-86,28; 214,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,76; 121,5</t>
+          <t>-73,48; 163,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 263,39</t>
+          <t>-63,61; 216,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,78; 337,47</t>
+          <t>-82,54; 492,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Estudios-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-81,21; 0,0</t>
+          <t>-80,48; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 21,0</t>
+          <t>-11,74; 21,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 18,81</t>
+          <t>-15,68; 21,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 13,7</t>
+          <t>-34,47; 13,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,31; 25,82</t>
+          <t>-49,99; 27,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,85; 487,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 361,84</t>
+          <t>-75,55; 380,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 50,42</t>
+          <t>-39,22; 48,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 58,0</t>
+          <t>-10,82; 58,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-62,38; 66,34</t>
+          <t>-63,58; 63,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 11,02</t>
+          <t>-15,24; 10,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 14,84</t>
+          <t>-18,34; 13,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 21,02</t>
+          <t>-20,5; 20,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 32,53</t>
+          <t>-33,12; 29,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,28; 214,12</t>
+          <t>-84,24; 212,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 163,44</t>
+          <t>-74,33; 143,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,61; 216,21</t>
+          <t>-63,23; 187,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 492,8</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-80,48; 0,0</t>
+          <t>-80,8; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-81,57; 0,0</t>
+          <t>-80,49; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-14,28</t>
+          <t>-15,74</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-48,68%</t>
+          <t>-48,65%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 21,54</t>
+          <t>-11,71; 23,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 21,38</t>
+          <t>-15,91; 17,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 13,53</t>
+          <t>-30,7; 15,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,99; 27,42</t>
+          <t>-49,19; 32,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,94; 606,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,55; 380,25</t>
+          <t>-75,94; 250,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>8,52</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 48,82</t>
+          <t>-39,01; 48,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 58,44</t>
+          <t>-10,72; 63,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-63,58; 63,55</t>
+          <t>-62,05; 64,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 10,26</t>
+          <t>-15,7; 9,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 13,43</t>
+          <t>-16,98; 12,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 20,86</t>
+          <t>-20,88; 22,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 29,51</t>
+          <t>-32,09; 34,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,24; 212,71</t>
+          <t>-84,34; 201,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,33; 143,92</t>
+          <t>-74,76; 121,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,23; 187,57</t>
+          <t>-64,46; 263,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 367,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-39,86</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-21,11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-64,37</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-64,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-39.85928242020413</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-21.10830768818759</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-64.37475901186241</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.643747590118624</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-80,8; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-80,49; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-80.80065105726788</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-80.48725871201363</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,39</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,01</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-8,9</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-15,74</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>30,44%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-44,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-48,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-11,71; 23,46</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-15,91; 17,85</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-30,7; 15,02</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-49,19; 32,21</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-75,94; 606,82</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-75,94; 250,65</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.39466476059634</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.009587180838609</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-8.903739190803606</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-15.74013704064592</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3043962078332547</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.06767783440297401</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.4420781110655225</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.4865027068845698</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-4,07</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>27,36</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-16,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>256,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>26,28%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-11.70676566003853</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-15.90669991698043</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-30.70353076552368</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-49.19475321144252</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7594157169725443</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7593566208775441</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-39,01; 48,26</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-10,72; 63,39</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-62,05; 64,75</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>23.45907478421529</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>17.85430873214063</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>15.02021503725573</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>32.20845780456892</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>6.068240042162444</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.506546791749895</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +783,175 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,55</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-20,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-13,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.071479506796521</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>27.35923111796236</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>8.515406682115934</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="n">
+        <v>-0.1618198387227195</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>2.563300607046786</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.2628297475838811</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-15,7; 9,7</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-16,98; 12,03</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-20,88; 22,2</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-32,09; 34,39</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-84,34; 201,84</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-74,76; 121,5</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-64,46; 263,39</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 367,54</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>-39.0094233237825</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-10.71554263516078</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-62.05405668535381</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>48.26453063674698</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>63.38603306508401</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>64.7484179749687</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.554704906982479</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.49521887869057</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.276135974439763</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.1949990453929296</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.208165500821786</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1384197247504137</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.06011278302960361</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.007363632267357125</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-15.69552620791438</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-16.97864242478489</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-20.88306294798407</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-32.08569542076016</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8433909072628978</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7475832540303866</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.644635578440933</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9.702580252170407</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>12.02827703860551</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>22.19962105568049</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>34.38706574460353</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.018416933832388</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.214969012487765</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.633865428977699</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>3.67537607925836</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +959,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
